--- a/config/generated/templates/Effect.xlsx
+++ b/config/generated/templates/Effect.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
   <si>
     <t>@table</t>
   </si>
@@ -43,7 +43,7 @@
     <t>@schema</t>
   </si>
   <si>
-    <t>0421727df8c5bbeb</t>
+    <t>1f5968342d107c2e</t>
   </si>
   <si>
     <t>#name</t>
@@ -73,6 +73,12 @@
     <t>magnitude_comparator_expression_id</t>
   </si>
   <si>
+    <t>dot_element</t>
+  </si>
+  <si>
+    <t>detonation_tag_identity_id</t>
+  </si>
+  <si>
     <t>snapshot_policy</t>
   </si>
   <si>
@@ -110,6 +116,12 @@
   </si>
   <si>
     <t>enum&lt;EffectStackPolicy&gt;</t>
+  </si>
+  <si>
+    <t>optional&lt;enum&lt;CombatElement&gt;&gt;</t>
+  </si>
+  <si>
+    <t>optional&lt;ref&lt;ContentIdentity.id&gt;&gt;</t>
   </si>
   <si>
     <t>enum&lt;SnapshotPolicy&gt;</t>
@@ -550,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -562,12 +574,14 @@
     <col min="8" max="8" width="21.7109375" style="5" customWidth="1"/>
     <col min="9" max="9" width="23.7109375" style="5" customWidth="1"/>
     <col min="10" max="10" width="32.7109375" style="5" customWidth="1"/>
-    <col min="11" max="11" width="20.7109375" style="5" customWidth="1"/>
-    <col min="12" max="12" width="26.7109375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="29.7109375" style="5" customWidth="1"/>
+    <col min="12" max="12" width="32.7109375" style="5" customWidth="1"/>
     <col min="13" max="13" width="20.7109375" style="5" customWidth="1"/>
+    <col min="14" max="14" width="26.7109375" style="5" customWidth="1"/>
+    <col min="15" max="15" width="20.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -599,7 +613,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="24" customHeight="1">
+    <row r="2" spans="1:15" ht="24" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>10</v>
       </c>
@@ -639,10 +653,16 @@
       <c r="M2" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="N2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:15">
       <c r="A3" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>5</v>
@@ -680,51 +700,63 @@
       <c r="M3" s="5" t="s">
         <v>21</v>
       </c>
+      <c r="N3" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:15">
       <c r="A4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G4" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:15">
       <c r="A5" s="4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>7</v>
@@ -762,18 +794,24 @@
       <c r="M5" s="5" t="s">
         <v>7</v>
       </c>
+      <c r="N5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="O5" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C6" s="5"/>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -782,13 +820,15 @@
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
-      <c r="M6" s="5" t="s">
-        <v>38</v>
+      <c r="M6" s="5"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="42" customHeight="1">
+    <row r="7" spans="1:15" ht="42" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -802,9 +842,11 @@
       <c r="K7" s="6"/>
       <c r="L7" s="6"/>
       <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
     </row>
   </sheetData>
-  <dataValidations count="9">
+  <dataValidations count="10">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Buff, Debuff, Control, Dot, Mark, Field, Shield, NeutralState" promptTitle="EffectCategory enum" prompt="Select a value from the dropdown." sqref="C8:C1007">
       <formula1>"Buff,Debuff,Control,Dot,Mark,Field,Shield,NeutralState"</formula1>
     </dataValidation>
@@ -824,13 +866,16 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Replace, Refresh, RefreshAndAddStacks, StrongestWins, IndependentBySource, IndependentInstances, UniqueGlobal, UniquePerSource" promptTitle="EffectStackPolicy enum" prompt="Select a value from the dropdown." sqref="I8:I1007">
       <formula1>"Replace,Refresh,RefreshAndAddStacks,StrongestWins,IndependentBySource,IndependentInstances,UniqueGlobal,UniquePerSource"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Dynamic, OnApplication, OnActionStart, OnPhaseStart, OnHitStart, SourceSnapshotTargetDynamic, SourceDynamicTargetSnapshot, RecomputeOnStackChange, ExplicitFields" promptTitle="SnapshotPolicy enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Physical, Fire, Ice, Lightning, Wind, Quantum, Imaginary" promptTitle="CombatElement enum" prompt="Select a value from the dropdown." sqref="K8:K1007">
+      <formula1>"Physical,Fire,Ice,Lightning,Wind,Quantum,Imaginary"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: Dynamic, OnApplication, OnActionStart, OnPhaseStart, OnHitStart, SourceSnapshotTargetDynamic, SourceDynamicTargetSnapshot, RecomputeOnStackChange, ExplicitFields" promptTitle="SnapshotPolicy enum" prompt="Select a value from the dropdown." sqref="M8:M1007">
       <formula1>"Dynamic,OnApplication,OnActionStart,OnPhaseStart,OnHitStart,SourceSnapshotTargetDynamic,SourceDynamicTargetSnapshot,RecomputeOnStackChange,ExplicitFields"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: RemoveWithOwner, TransferToTeam, FreezeSnapshot, PersistByScope, ExplicitRule" promptTitle="EffectTeardownPolicy enum" prompt="Select a value from the dropdown." sqref="L8:L1007">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid enum value" error="Value must be one of: RemoveWithOwner, TransferToTeam, FreezeSnapshot, PersistByScope, ExplicitRule" promptTitle="EffectTeardownPolicy enum" prompt="Select a value from the dropdown." sqref="N8:N1007">
       <formula1>"RemoveWithOwner,TransferToTeam,FreezeSnapshot,PersistByScope,ExplicitRule"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from -1000000 to 1000000." promptTitle="Integer range" prompt="Enter an integer from -1000000 to 1000000." sqref="M8:M1007">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Value outside range" error="Value must be an integer from -1000000 to 1000000." promptTitle="Integer range" prompt="Enter an integer from -1000000 to 1000000." sqref="O8:O1007">
       <formula1>-1000000</formula1>
       <formula2>1000000</formula2>
     </dataValidation>

--- a/config/generated/templates/Effect.xlsx
+++ b/config/generated/templates/Effect.xlsx
@@ -34,16 +34,16 @@
     <t>id</t>
   </si>
   <si>
-    <t>@scope</t>
-  </si>
-  <si>
-    <t>all</t>
+    <t>@groups</t>
+  </si>
+  <si>
+    <t>common</t>
   </si>
   <si>
     <t>@schema</t>
   </si>
   <si>
-    <t>1f5968342d107c2e</t>
+    <t>cfcafcf302fc412e</t>
   </si>
   <si>
     <t>#name</t>
@@ -130,7 +130,7 @@
     <t>enum&lt;EffectTeardownPolicy&gt;</t>
   </si>
   <si>
-    <t>#scope</t>
+    <t>#groups</t>
   </si>
   <si>
     <t>#input</t>
